--- a/site/Entra-ID-Procore-Integration-Guide/headings.xlsx
+++ b/site/Entra-ID-Procore-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,6 +438,578 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Overview</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>h_01JZW9E9B6ZZRTWQSYHXT2DAAF</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#h_01JZW9E9B6ZZRTWQSYHXT2DAAF</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Key Functions</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>h_01K06FVR3HAYYM66WATF77B0B4</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#h_01K06FVR3HAYYM66WATF77B0B4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Prerequisites</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>h_01JZW70JA70W2SCAXXM5NFYAK0</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#h_01JZW70JA70W2SCAXXM5NFYAK0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Integration Setup</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>h_01F6EH0W486EMXD6A000X2Z4YZ</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#h_01F6EH0W486EMXD6A000X2Z4YZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Create Integration</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>h_01HXY3TX2QHXF1YJK3GCQQ87P7</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#h_01HXY3TX2QHXF1YJK3GCQQ87P7</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Configuration</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>h_01JPQ8ZTEY7NJC2SRMDWPK964A</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#h_01JPQ8ZTEY7NJC2SRMDWPK964A</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Applications</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>h_01JPQ91FKVZHN9SQJEN1N0S3XQ</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#h_01JPQ91FKVZHN9SQJEN1N0S3XQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Parameters</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Integration Scenarios</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>h_01K04AVZNHW4RD086HGMDCJSM6</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#h_01K04AVZNHW4RD086HGMDCJSM6</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>General Settings</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>01KF2RH05MP5RR93W69VEMT2AR</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#01KF2RH05MP5RR93W69VEMT2AR</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>User Management</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>01K593846FCRSW60E8KGDZ0K4A</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#01K593846FCRSW60E8KGDZ0K4A</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>User Provisioning Settings</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>01KF2ST6Y7GH70E2MJCYT5X2DZ</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#01KF2ST6Y7GH70E2MJCYT5X2DZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>User Provisioning Threshold Settings</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>01KF2STBQHQZSSRVHSD95EW224</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#01KF2STBQHQZSSRVHSD95EW224</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Create User Settings</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>h_01KGPAMEAW55WS81E8WGSSTNW2</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#h_01KGPAMEAW55WS81E8WGSSTNW2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Update User Settings</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>h_01KGPAMEAWGD83B6WJD2G64H6F</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#h_01KGPAMEAWGD83B6WJD2G64H6F</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>01KFD0RVZ9EM5G97GM5P4XPJHZ</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#01KFD0RVZ9EM5G97GM5P4XPJHZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Offboarding</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>h_01KGPAMEAWJDEJ5ZJJRVVJHBR8</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#h_01KGPAMEAWJDEJ5ZJJRVVJHBR8</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Logging</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Reporting</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Log Insights</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Attribute Map</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>h_01KC15BBW7VM3TXVTH7W8GHAP3</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#h_01KC15BBW7VM3TXVTH7W8GHAP3</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>01JVC7QW1983644JGH2WGK8FWX</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#01JVC7QW1983644JGH2WGK8FWX</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>01KF2S3B9ZMTA5NXEEMGJ3MX5B</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#01KF2S3B9ZMTA5NXEEMGJ3MX5B</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/Entra-ID-Procore-Integration-Guide/headings.xlsx
+++ b/site/Entra-ID-Procore-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>User Provisioning Settings</t>
+          <t>User Provisioning Threshold Settings</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -693,85 +693,85 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>01KF2ST6Y7GH70E2MJCYT5X2DZ</t>
+          <t>01KF2STBQHQZSSRVHSD95EW224</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#01KF2ST6Y7GH70E2MJCYT5X2DZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#01KF2STBQHQZSSRVHSD95EW224</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>User Provisioning Threshold Settings</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>01KF2STBQHQZSSRVHSD95EW224</t>
+          <t>h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#01KF2STBQHQZSSRVHSD95EW224</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Create User Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KGPAMEAW55WS81E8WGSSTNW2</t>
+          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#h_01KGPAMEAW55WS81E8WGSSTNW2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Update User Settings</t>
+          <t>Notification Settings</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KGPAMEAWGD83B6WJD2G64H6F</t>
+          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#h_01KGPAMEAWGD83B6WJD2G64H6F</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Onboarding</t>
+          <t>Log Insights Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -781,230 +781,98 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>01KFD0RVZ9EM5G97GM5P4XPJHZ</t>
+          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#01KFD0RVZ9EM5G97GM5P4XPJHZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Offboarding</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KGPAMEAWJDEJ5ZJJRVVJHBR8</t>
+          <t>h_01KC15BBW7VM3TXVTH7W8GHAP3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#h_01KGPAMEAWJDEJ5ZJJRVVJHBR8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#h_01KC15BBW7VM3TXVTH7W8GHAP3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Logging</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
+          <t>01KF2S3B9ZMTA5NXEEMGJ3MX5B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#01KF2S3B9ZMTA5NXEEMGJ3MX5B</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Reporting</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Additional Options</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Log Insights</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Attribute Map</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>h_01KC15BBW7VM3TXVTH7W8GHAP3</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#h_01KC15BBW7VM3TXVTH7W8GHAP3</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Tables</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>01JVC7QW1983644JGH2WGK8FWX</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#01JVC7QW1983644JGH2WGK8FWX</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Schedule</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>01KF2S3B9ZMTA5NXEEMGJ3MX5B</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#01KF2S3B9ZMTA5NXEEMGJ3MX5B</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Execute Integration</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Additional Options</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/Entra-ID-Procore-Integration-Guide/headings.xlsx
+++ b/site/Entra-ID-Procore-Integration-Guide/headings.xlsx
@@ -683,7 +683,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>User Provisioning Threshold Settings</t>
+          <t>Source Settings</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -771,7 +771,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Log Insights Settings</t>
+          <t>Log Insight Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">

--- a/site/Entra-ID-Procore-Integration-Guide/headings.xlsx
+++ b/site/Entra-ID-Procore-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -705,29 +705,29 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Target Settings</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
+          <t>h_01KJ9X1KBMETDBKVYM3C75KSQ8</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#h_01KJ9X1KBMETDBKVYM3C75KSQ8</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,19 +737,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Notification Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,19 +759,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Log Insight Settings</t>
+          <t>Notification Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -781,41 +781,41 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Log Insight Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KC15BBW7VM3TXVTH7W8GHAP3</t>
+          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#h_01KC15BBW7VM3TXVTH7W8GHAP3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,54 +825,76 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>01KF2S3B9ZMTA5NXEEMGJ3MX5B</t>
+          <t>h_01KC15BBW7VM3TXVTH7W8GHAP3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#01KF2S3B9ZMTA5NXEEMGJ3MX5B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#h_01KC15BBW7VM3TXVTH7W8GHAP3</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>01KF2S3B9ZMTA5NXEEMGJ3MX5B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#01KF2S3B9ZMTA5NXEEMGJ3MX5B</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/Entra-ID-Procore-Integration-Guide/headings.xlsx
+++ b/site/Entra-ID-Procore-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -715,19 +715,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KJ9X1KBMETDBKVYM3C75KSQ8</t>
+          <t>h_01KJA16D68S6Q9ZCW31V9VXBX7</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#h_01KJ9X1KBMETDBKVYM3C75KSQ8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#h_01KJA16D68S6Q9ZCW31V9VXBX7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Debug Mode</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -749,7 +749,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,19 +759,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>h_01KJA16D68SX7XZB397PAECRT8</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#h_01KJA16D68SX7XZB397PAECRT8</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Notification Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -781,19 +781,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Log Insight Settings</t>
+          <t>Notification Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,41 +803,41 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Log Insight Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KC15BBW7VM3TXVTH7W8GHAP3</t>
+          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#h_01KC15BBW7VM3TXVTH7W8GHAP3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,54 +847,76 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>01KF2S3B9ZMTA5NXEEMGJ3MX5B</t>
+          <t>h_01KC15BBW7VM3TXVTH7W8GHAP3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#01KF2S3B9ZMTA5NXEEMGJ3MX5B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#h_01KC15BBW7VM3TXVTH7W8GHAP3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>01KF2S3B9ZMTA5NXEEMGJ3MX5B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#01KF2S3B9ZMTA5NXEEMGJ3MX5B</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/Entra-ID-Procore-Integration-Guide/headings.xlsx
+++ b/site/Entra-ID-Procore-Integration-Guide/headings.xlsx
@@ -715,12 +715,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KJA16D68S6Q9ZCW31V9VXBX7</t>
+          <t>h_01KJA66XMSEP7NHJMR5090KH3R</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#h_01KJA16D68S6Q9ZCW31V9VXBX7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#h_01KJA66XMSEP7NHJMR5090KH3R</t>
         </is>
       </c>
     </row>
@@ -759,12 +759,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KJA16D68SX7XZB397PAECRT8</t>
+          <t>h_01KJA66XMS9JRCHM000N2J4R39</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#h_01KJA16D68SX7XZB397PAECRT8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Procore-Integration-Guide/#h_01KJA66XMS9JRCHM000N2J4R39</t>
         </is>
       </c>
     </row>

--- a/site/Entra-ID-Procore-Integration-Guide/headings.xlsx
+++ b/site/Entra-ID-Procore-Integration-Guide/headings.xlsx
@@ -683,7 +683,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Source Settings</t>
+          <t>Entra ID Settings</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -705,7 +705,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Target Settings</t>
+          <t>Procore Settings</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
